--- a/astro-site/public/dl/catering-checklist-templates/02-catering-transport-delivery-checklist.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/02-catering-transport-delivery-checklist.xlsx
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Hold the cold chain the whole trip: cold 41 °F or below, hot 135 °F or above. Anything traveling without temperature control goes under time as a public health control (FDA Food Code 3-501.19): 4 h max from the marked departure time</t>
+          <t>Hold the cold chain the whole trip: cold 41 °F or below, hot 135 °F or above. Anything traveling without temperature control goes under time as a public health control (FDA Food Code 3-501.19, written procedure required): mark the time it left 41 °F / 135 °F; the 4 h include the trip AND the service at the venue, and whatever is left at 4 h is discarded</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -1358,7 +1358,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G38">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
